--- a/r4-core-151-gda-triple/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r4-core-151-gda-triple/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T14:14:36+00:00</t>
+    <t>2026-10-19T12:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-151-gda-triple/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r4-core-151-gda-triple/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T12:51:52+00:00</t>
+    <t>2026-10-19T13:41:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
